--- a/data/trans_bre/P16A_n_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,51</t>
+          <t>0,26; 3,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,58</t>
+          <t>3,89; 8,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,31</t>
+          <t>2,38; 7,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,88; 15,74</t>
+          <t>8,84; 15,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 147,38</t>
+          <t>2,45; 138,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,87; 255,63</t>
+          <t>66,62; 249,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,4; 181,93</t>
+          <t>36,31; 179,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60,84; 143,26</t>
+          <t>59,97; 148,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,36</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,45</t>
+          <t>0,16; 1,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,39</t>
+          <t>0,82; 2,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,31</t>
+          <t>0,22; 3,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 329,96</t>
+          <t>-5,1; 354,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 387,85</t>
+          <t>9,14; 438,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,38; 519,94</t>
+          <t>68,08; 473,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 129,98</t>
+          <t>6,93; 132,36</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,15</t>
+          <t>-1,67; 0,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,42</t>
+          <t>-1,5; 2,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,3</t>
+          <t>-0,47; 2,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,1</t>
+          <t>-0,14; 3,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,18; inf</t>
+          <t>-69,9; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,91; 1201,93</t>
+          <t>-81,43; 978,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 184,13</t>
+          <t>-8,78; 182,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,81</t>
+          <t>0,42; 1,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,04</t>
+          <t>2,37; 4,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,43</t>
+          <t>1,77; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,89</t>
+          <t>2,7; 5,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 147,9</t>
+          <t>21,21; 149,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>106,13; 289,78</t>
+          <t>102,83; 284,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,59; 255,43</t>
+          <t>86,31; 268,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,22; 155,14</t>
+          <t>57,43; 149,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R3-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R3-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>103,17%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,35</t>
+          <t>0,28; 3,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,58</t>
+          <t>4,15; 8,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,34</t>
+          <t>2,22; 7,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 15,97</t>
+          <t>9,14; 15,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 138,58</t>
+          <t>4,48; 144,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,62; 249,35</t>
+          <t>71,79; 263,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,31; 179,18</t>
+          <t>34,05; 179,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,97; 148,25</t>
+          <t>64,48; 151,69</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,03; 1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,51</t>
+          <t>0,15; 1,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,34</t>
+          <t>0,83; 2,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,29</t>
+          <t>1,24; 3,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 354,24</t>
+          <t>-2,3; 336,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 438,84</t>
+          <t>10,8; 399,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,08; 473,37</t>
+          <t>71,46; 570,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 132,36</t>
+          <t>28,99; 113,32</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,09</t>
+          <t>-1,63; 0,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,46</t>
+          <t>-1,42; 2,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,27</t>
+          <t>-0,41; 2,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,0</t>
+          <t>-0,12; 2,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,9; —</t>
+          <t>-64,45; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-81,43; 978,49</t>
+          <t>-68,85; 1169,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 182,42</t>
+          <t>-4,33; 176,67</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>100,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,8</t>
+          <t>0,46; 1,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,05</t>
+          <t>2,19; 4,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,51</t>
+          <t>1,8; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,82</t>
+          <t>3,77; 5,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,21; 149,55</t>
+          <t>22,95; 147,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>102,83; 284,45</t>
+          <t>92,7; 270,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,31; 268,31</t>
+          <t>84,99; 250,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,43; 149,6</t>
+          <t>70,18; 132,7</t>
         </is>
       </c>
     </row>
